--- a/ClosedXML.Tests/Resource/Examples/Misc/AdjustToContents.xlsx
+++ b/ClosedXML.Tests/Resource/Examples/Misc/AdjustToContents.xlsx
@@ -3401,12 +3401,12 @@
     <x:col min="2" max="2" width="28.190625" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:2" customFormat="1" ht="41.5039" customHeight="1">
+    <x:row r="1" spans="1:2" ht="41.5039" customHeight="1">
       <x:c r="A1" s="1" t="s">
         <x:v>0</x:v>
       </x:c>
     </x:row>
-    <x:row r="2" spans="1:2" customFormat="1" ht="27.669267" customHeight="1">
+    <x:row r="2" spans="1:2" ht="27.669267" customHeight="1">
       <x:c r="A2" s="2" t="s">
         <x:v>1</x:v>
       </x:c>
@@ -3650,97 +3650,97 @@
   <x:dimension ref="A1:A19"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
-    <x:row r="1" spans="1:1" customFormat="1" ht="304.361925" customHeight="1">
+    <x:row r="1" spans="1:1" ht="304.361925" customHeight="1">
       <x:c r="A1" s="3" t="s">
         <x:v>6</x:v>
       </x:c>
     </x:row>
-    <x:row r="2" spans="1:1" customFormat="1" ht="15.218096" customHeight="1">
+    <x:row r="2" spans="1:1" ht="15.218096" customHeight="1">
       <x:c r="A2" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
     </x:row>
-    <x:row r="3" spans="1:1" customFormat="1" ht="7.609048" customHeight="1">
+    <x:row r="3" spans="1:1" ht="7.609048" customHeight="1">
       <x:c r="A3" s="4" t="s">
         <x:v>8</x:v>
       </x:c>
     </x:row>
-    <x:row r="4" spans="1:1" customFormat="1" ht="16.063546" customHeight="1">
+    <x:row r="4" spans="1:1" ht="16.063546" customHeight="1">
       <x:c r="A4" s="5" t="s">
         <x:v>9</x:v>
       </x:c>
     </x:row>
-    <x:row r="5" spans="1:1" customFormat="1" ht="24.095319" customHeight="1">
+    <x:row r="5" spans="1:1" ht="24.095319" customHeight="1">
       <x:c r="A5" s="6" t="s">
         <x:v>10</x:v>
       </x:c>
     </x:row>
-    <x:row r="6" spans="1:1" customFormat="1" ht="32.127092" customHeight="1">
+    <x:row r="6" spans="1:1" ht="32.127092" customHeight="1">
       <x:c r="A6" s="7" t="s">
         <x:v>11</x:v>
       </x:c>
     </x:row>
-    <x:row r="7" spans="1:1" customFormat="1" ht="40.158865" customHeight="1">
+    <x:row r="7" spans="1:1" ht="40.158865" customHeight="1">
       <x:c r="A7" s="8" t="s">
         <x:v>12</x:v>
       </x:c>
     </x:row>
-    <x:row r="8" spans="1:1" customFormat="1" ht="48.190638" customHeight="1">
+    <x:row r="8" spans="1:1" ht="48.190638" customHeight="1">
       <x:c r="A8" s="9" t="s">
         <x:v>13</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" spans="1:1" customFormat="1" ht="56.222411" customHeight="1">
+    <x:row r="9" spans="1:1" ht="56.222411" customHeight="1">
       <x:c r="A9" s="10" t="s">
         <x:v>14</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" spans="1:1" customFormat="1" ht="64.254184" customHeight="1">
+    <x:row r="10" spans="1:1" ht="64.254184" customHeight="1">
       <x:c r="A10" s="11" t="s">
         <x:v>15</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" spans="1:1" customFormat="1" ht="72.285957" customHeight="1">
+    <x:row r="11" spans="1:1" ht="72.285957" customHeight="1">
       <x:c r="A11" s="12" t="s">
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" spans="1:1" customFormat="1" ht="80.31773" customHeight="1">
+    <x:row r="12" spans="1:1" ht="80.31773" customHeight="1">
       <x:c r="A12" s="13" t="s">
         <x:v>17</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" spans="1:1" customFormat="1" ht="88.349503" customHeight="1">
+    <x:row r="13" spans="1:1" ht="88.349503" customHeight="1">
       <x:c r="A13" s="14" t="s">
         <x:v>18</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" spans="1:1" customFormat="1" ht="96.381276" customHeight="1">
+    <x:row r="14" spans="1:1" ht="96.381276" customHeight="1">
       <x:c r="A14" s="15" t="s">
         <x:v>19</x:v>
       </x:c>
     </x:row>
-    <x:row r="15" spans="1:1" customFormat="1" ht="104.413049" customHeight="1">
+    <x:row r="15" spans="1:1" ht="104.413049" customHeight="1">
       <x:c r="A15" s="16" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
-    <x:row r="16" spans="1:1" customFormat="1" ht="112.444822" customHeight="1">
+    <x:row r="16" spans="1:1" ht="112.444822" customHeight="1">
       <x:c r="A16" s="17" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
-    <x:row r="17" spans="1:1" customFormat="1" ht="120.476595" customHeight="1">
+    <x:row r="17" spans="1:1" ht="120.476595" customHeight="1">
       <x:c r="A17" s="18" t="s">
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="18" spans="1:1" customFormat="1" ht="128.508368" customHeight="1">
+    <x:row r="18" spans="1:1" ht="128.508368" customHeight="1">
       <x:c r="A18" s="19" t="s">
         <x:v>23</x:v>
       </x:c>
     </x:row>
-    <x:row r="19" spans="1:1" customFormat="1" ht="136.540141" customHeight="1">
+    <x:row r="19" spans="1:1" ht="136.540141" customHeight="1">
       <x:c r="A19" s="20" t="s">
         <x:v>24</x:v>
       </x:c>
@@ -3762,97 +3762,97 @@
   <x:dimension ref="A1:A19"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
-    <x:row r="1" spans="1:1" customFormat="1" ht="304.361925" customHeight="1">
+    <x:row r="1" spans="1:1" ht="304.361925" customHeight="1">
       <x:c r="A1" s="3" t="s">
         <x:v>6</x:v>
       </x:c>
     </x:row>
-    <x:row r="2" spans="1:1" customFormat="1" ht="83.0078" customHeight="1">
+    <x:row r="2" spans="1:1" ht="83.0078" customHeight="1">
       <x:c r="A2" s="0" t="s">
         <x:v>43</x:v>
       </x:c>
     </x:row>
-    <x:row r="3" spans="1:1" customFormat="1" ht="17.293292" customHeight="1">
+    <x:row r="3" spans="1:1" ht="17.293292" customHeight="1">
       <x:c r="A3" s="4" t="s">
         <x:v>44</x:v>
       </x:c>
     </x:row>
-    <x:row r="4" spans="1:1" customFormat="1" ht="34.586583" customHeight="1">
+    <x:row r="4" spans="1:1" ht="34.586583" customHeight="1">
       <x:c r="A4" s="5" t="s">
         <x:v>45</x:v>
       </x:c>
     </x:row>
-    <x:row r="5" spans="1:1" customFormat="1" ht="51.879875" customHeight="1">
+    <x:row r="5" spans="1:1" ht="51.879875" customHeight="1">
       <x:c r="A5" s="6" t="s">
         <x:v>46</x:v>
       </x:c>
     </x:row>
-    <x:row r="6" spans="1:1" customFormat="1" ht="69.173166" customHeight="1">
+    <x:row r="6" spans="1:1" ht="69.173166" customHeight="1">
       <x:c r="A6" s="7" t="s">
         <x:v>47</x:v>
       </x:c>
     </x:row>
-    <x:row r="7" spans="1:1" customFormat="1" ht="86.466458" customHeight="1">
+    <x:row r="7" spans="1:1" ht="86.466458" customHeight="1">
       <x:c r="A7" s="8" t="s">
         <x:v>48</x:v>
       </x:c>
     </x:row>
-    <x:row r="8" spans="1:1" customFormat="1" ht="103.759749" customHeight="1">
+    <x:row r="8" spans="1:1" ht="103.759749" customHeight="1">
       <x:c r="A8" s="9" t="s">
         <x:v>49</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" spans="1:1" customFormat="1" ht="121.053041" customHeight="1">
+    <x:row r="9" spans="1:1" ht="121.053041" customHeight="1">
       <x:c r="A9" s="10" t="s">
         <x:v>50</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" spans="1:1" customFormat="1" ht="138.346333" customHeight="1">
+    <x:row r="10" spans="1:1" ht="138.346333" customHeight="1">
       <x:c r="A10" s="11" t="s">
         <x:v>51</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" spans="1:1" customFormat="1" ht="155.639624" customHeight="1">
+    <x:row r="11" spans="1:1" ht="155.639624" customHeight="1">
       <x:c r="A11" s="12" t="s">
         <x:v>52</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" spans="1:1" customFormat="1" ht="172.932916" customHeight="1">
+    <x:row r="12" spans="1:1" ht="172.932916" customHeight="1">
       <x:c r="A12" s="13" t="s">
         <x:v>53</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" spans="1:1" customFormat="1" ht="190.226207" customHeight="1">
+    <x:row r="13" spans="1:1" ht="190.226207" customHeight="1">
       <x:c r="A13" s="14" t="s">
         <x:v>54</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" spans="1:1" customFormat="1" ht="207.519499" customHeight="1">
+    <x:row r="14" spans="1:1" ht="207.519499" customHeight="1">
       <x:c r="A14" s="15" t="s">
         <x:v>55</x:v>
       </x:c>
     </x:row>
-    <x:row r="15" spans="1:1" customFormat="1" ht="224.81279" customHeight="1">
+    <x:row r="15" spans="1:1" ht="224.81279" customHeight="1">
       <x:c r="A15" s="16" t="s">
         <x:v>56</x:v>
       </x:c>
     </x:row>
-    <x:row r="16" spans="1:1" customFormat="1" ht="242.106082" customHeight="1">
+    <x:row r="16" spans="1:1" ht="242.106082" customHeight="1">
       <x:c r="A16" s="17" t="s">
         <x:v>57</x:v>
       </x:c>
     </x:row>
-    <x:row r="17" spans="1:1" customFormat="1" ht="259.399374" customHeight="1">
+    <x:row r="17" spans="1:1" ht="259.399374" customHeight="1">
       <x:c r="A17" s="18" t="s">
         <x:v>58</x:v>
       </x:c>
     </x:row>
-    <x:row r="18" spans="1:1" customFormat="1" ht="276.692665" customHeight="1">
+    <x:row r="18" spans="1:1" ht="276.692665" customHeight="1">
       <x:c r="A18" s="19" t="s">
         <x:v>59</x:v>
       </x:c>
     </x:row>
-    <x:row r="19" spans="1:1" customFormat="1" ht="293.985957" customHeight="1">
+    <x:row r="19" spans="1:1" ht="293.985957" customHeight="1">
       <x:c r="A19" s="20" t="s">
         <x:v>60</x:v>
       </x:c>

--- a/ClosedXML.Tests/Resource/Examples/Misc/AdjustToContents.xlsx
+++ b/ClosedXML.Tests/Resource/Examples/Misc/AdjustToContents.xlsx
@@ -3401,12 +3401,12 @@
     <x:col min="2" max="2" width="28.190625" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:2" ht="41.5039" customHeight="1">
+    <x:row r="1" spans="1:2" ht="44.677734" customHeight="1">
       <x:c r="A1" s="1" t="s">
         <x:v>0</x:v>
       </x:c>
     </x:row>
-    <x:row r="2" spans="1:2" ht="27.669267" customHeight="1">
+    <x:row r="2" spans="1:2" ht="29.785156" customHeight="1">
       <x:c r="A2" s="2" t="s">
         <x:v>1</x:v>
       </x:c>
@@ -3554,24 +3554,24 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="2.930625" style="0" customWidth="1"/>
-    <x:col min="2" max="2" width="51.020625" style="0" customWidth="1"/>
-    <x:col min="3" max="3" width="61.832986" style="0" customWidth="1"/>
-    <x:col min="4" max="4" width="61.271495" style="0" customWidth="1"/>
-    <x:col min="5" max="5" width="60.340427" style="0" customWidth="1"/>
-    <x:col min="6" max="6" width="59.046868" style="0" customWidth="1"/>
-    <x:col min="7" max="7" width="57.400662" style="0" customWidth="1"/>
-    <x:col min="8" max="8" width="55.414338" style="0" customWidth="1"/>
-    <x:col min="9" max="9" width="53.103012" style="0" customWidth="1"/>
-    <x:col min="10" max="10" width="50.484276" style="0" customWidth="1"/>
-    <x:col min="11" max="11" width="47.57806" style="0" customWidth="1"/>
-    <x:col min="12" max="12" width="44.406482" style="0" customWidth="1"/>
-    <x:col min="13" max="13" width="40.993679" style="0" customWidth="1"/>
-    <x:col min="14" max="14" width="37.365625" style="0" customWidth="1"/>
-    <x:col min="15" max="15" width="33.549931" style="0" customWidth="1"/>
-    <x:col min="16" max="16" width="29.575638" style="0" customWidth="1"/>
-    <x:col min="17" max="17" width="25.472992" style="0" customWidth="1"/>
-    <x:col min="18" max="18" width="21.273217" style="0" customWidth="1"/>
-    <x:col min="19" max="19" width="17.008275" style="0" customWidth="1"/>
+    <x:col min="2" max="2" width="49.890625" style="0" customWidth="1"/>
+    <x:col min="3" max="3" width="60.107286" style="0" customWidth="1"/>
+    <x:col min="4" max="4" width="59.558663" style="0" customWidth="1"/>
+    <x:col min="5" max="5" width="58.648931" style="0" customWidth="1"/>
+    <x:col min="6" max="6" width="57.385015" style="0" customWidth="1"/>
+    <x:col min="7" max="7" width="55.776534" style="0" customWidth="1"/>
+    <x:col min="8" max="8" width="53.835729" style="0" customWidth="1"/>
+    <x:col min="9" max="9" width="51.57737" style="0" customWidth="1"/>
+    <x:col min="10" max="10" width="49.018646" style="0" customWidth="1"/>
+    <x:col min="11" max="11" width="46.17903" style="0" customWidth="1"/>
+    <x:col min="12" max="12" width="43.080132" style="0" customWidth="1"/>
+    <x:col min="13" max="13" width="39.745538" style="0" customWidth="1"/>
+    <x:col min="14" max="14" width="36.200625" style="0" customWidth="1"/>
+    <x:col min="15" max="15" width="32.472373" style="0" customWidth="1"/>
+    <x:col min="16" max="16" width="28.589156" style="0" customWidth="1"/>
+    <x:col min="17" max="17" width="24.580527" style="0" customWidth="1"/>
+    <x:col min="18" max="18" width="20.476994" style="0" customWidth="1"/>
+    <x:col min="19" max="19" width="16.309789" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:19">
@@ -3650,97 +3650,97 @@
   <x:dimension ref="A1:A19"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
-    <x:row r="1" spans="1:1" ht="304.361925" customHeight="1">
+    <x:row r="1" spans="1:1" ht="327.636719" customHeight="1">
       <x:c r="A1" s="3" t="s">
         <x:v>6</x:v>
       </x:c>
     </x:row>
-    <x:row r="2" spans="1:1" ht="15.218096" customHeight="1">
+    <x:row r="2" spans="1:1" ht="16.381836" customHeight="1">
       <x:c r="A2" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
     </x:row>
-    <x:row r="3" spans="1:1" ht="7.609048" customHeight="1">
+    <x:row r="3" spans="1:1" ht="8.190918" customHeight="1">
       <x:c r="A3" s="4" t="s">
         <x:v>8</x:v>
       </x:c>
     </x:row>
-    <x:row r="4" spans="1:1" ht="16.063546" customHeight="1">
+    <x:row r="4" spans="1:1" ht="17.291938" customHeight="1">
       <x:c r="A4" s="5" t="s">
         <x:v>9</x:v>
       </x:c>
     </x:row>
-    <x:row r="5" spans="1:1" ht="24.095319" customHeight="1">
+    <x:row r="5" spans="1:1" ht="25.937907" customHeight="1">
       <x:c r="A5" s="6" t="s">
         <x:v>10</x:v>
       </x:c>
     </x:row>
-    <x:row r="6" spans="1:1" ht="32.127092" customHeight="1">
+    <x:row r="6" spans="1:1" ht="34.583876" customHeight="1">
       <x:c r="A6" s="7" t="s">
         <x:v>11</x:v>
       </x:c>
     </x:row>
-    <x:row r="7" spans="1:1" ht="40.158865" customHeight="1">
+    <x:row r="7" spans="1:1" ht="43.229845" customHeight="1">
       <x:c r="A7" s="8" t="s">
         <x:v>12</x:v>
       </x:c>
     </x:row>
-    <x:row r="8" spans="1:1" ht="48.190638" customHeight="1">
+    <x:row r="8" spans="1:1" ht="51.875814" customHeight="1">
       <x:c r="A8" s="9" t="s">
         <x:v>13</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" spans="1:1" ht="56.222411" customHeight="1">
+    <x:row r="9" spans="1:1" ht="60.521783" customHeight="1">
       <x:c r="A9" s="10" t="s">
         <x:v>14</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" spans="1:1" ht="64.254184" customHeight="1">
+    <x:row r="10" spans="1:1" ht="69.167752" customHeight="1">
       <x:c r="A10" s="11" t="s">
         <x:v>15</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" spans="1:1" ht="72.285957" customHeight="1">
+    <x:row r="11" spans="1:1" ht="77.813721" customHeight="1">
       <x:c r="A11" s="12" t="s">
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" spans="1:1" ht="80.31773" customHeight="1">
+    <x:row r="12" spans="1:1" ht="86.45969" customHeight="1">
       <x:c r="A12" s="13" t="s">
         <x:v>17</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" spans="1:1" ht="88.349503" customHeight="1">
+    <x:row r="13" spans="1:1" ht="95.105659" customHeight="1">
       <x:c r="A13" s="14" t="s">
         <x:v>18</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" spans="1:1" ht="96.381276" customHeight="1">
+    <x:row r="14" spans="1:1" ht="103.751628" customHeight="1">
       <x:c r="A14" s="15" t="s">
         <x:v>19</x:v>
       </x:c>
     </x:row>
-    <x:row r="15" spans="1:1" ht="104.413049" customHeight="1">
+    <x:row r="15" spans="1:1" ht="112.397597" customHeight="1">
       <x:c r="A15" s="16" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
-    <x:row r="16" spans="1:1" ht="112.444822" customHeight="1">
+    <x:row r="16" spans="1:1" ht="121.043566" customHeight="1">
       <x:c r="A16" s="17" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
-    <x:row r="17" spans="1:1" ht="120.476595" customHeight="1">
+    <x:row r="17" spans="1:1" ht="129.689535" customHeight="1">
       <x:c r="A17" s="18" t="s">
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="18" spans="1:1" ht="128.508368" customHeight="1">
+    <x:row r="18" spans="1:1" ht="138.335503" customHeight="1">
       <x:c r="A18" s="19" t="s">
         <x:v>23</x:v>
       </x:c>
     </x:row>
-    <x:row r="19" spans="1:1" ht="136.540141" customHeight="1">
+    <x:row r="19" spans="1:1" ht="146.981472" customHeight="1">
       <x:c r="A19" s="20" t="s">
         <x:v>24</x:v>
       </x:c>
@@ -3762,97 +3762,97 @@
   <x:dimension ref="A1:A19"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
-    <x:row r="1" spans="1:1" ht="304.361925" customHeight="1">
+    <x:row r="1" spans="1:1" ht="327.636719" customHeight="1">
       <x:c r="A1" s="3" t="s">
         <x:v>6</x:v>
       </x:c>
     </x:row>
-    <x:row r="2" spans="1:1" ht="83.0078" customHeight="1">
+    <x:row r="2" spans="1:1" ht="89.355469" customHeight="1">
       <x:c r="A2" s="0" t="s">
         <x:v>43</x:v>
       </x:c>
     </x:row>
-    <x:row r="3" spans="1:1" ht="17.293292" customHeight="1">
+    <x:row r="3" spans="1:1" ht="18.615723" customHeight="1">
       <x:c r="A3" s="4" t="s">
         <x:v>44</x:v>
       </x:c>
     </x:row>
-    <x:row r="4" spans="1:1" ht="34.586583" customHeight="1">
+    <x:row r="4" spans="1:1" ht="37.231445" customHeight="1">
       <x:c r="A4" s="5" t="s">
         <x:v>45</x:v>
       </x:c>
     </x:row>
-    <x:row r="5" spans="1:1" ht="51.879875" customHeight="1">
+    <x:row r="5" spans="1:1" ht="55.847168" customHeight="1">
       <x:c r="A5" s="6" t="s">
         <x:v>46</x:v>
       </x:c>
     </x:row>
-    <x:row r="6" spans="1:1" ht="69.173166" customHeight="1">
+    <x:row r="6" spans="1:1" ht="74.462891" customHeight="1">
       <x:c r="A6" s="7" t="s">
         <x:v>47</x:v>
       </x:c>
     </x:row>
-    <x:row r="7" spans="1:1" ht="86.466458" customHeight="1">
+    <x:row r="7" spans="1:1" ht="93.078613" customHeight="1">
       <x:c r="A7" s="8" t="s">
         <x:v>48</x:v>
       </x:c>
     </x:row>
-    <x:row r="8" spans="1:1" ht="103.759749" customHeight="1">
+    <x:row r="8" spans="1:1" ht="111.694336" customHeight="1">
       <x:c r="A8" s="9" t="s">
         <x:v>49</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" spans="1:1" ht="121.053041" customHeight="1">
+    <x:row r="9" spans="1:1" ht="130.310059" customHeight="1">
       <x:c r="A9" s="10" t="s">
         <x:v>50</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" spans="1:1" ht="138.346333" customHeight="1">
+    <x:row r="10" spans="1:1" ht="148.925781" customHeight="1">
       <x:c r="A10" s="11" t="s">
         <x:v>51</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" spans="1:1" ht="155.639624" customHeight="1">
+    <x:row r="11" spans="1:1" ht="167.541504" customHeight="1">
       <x:c r="A11" s="12" t="s">
         <x:v>52</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" spans="1:1" ht="172.932916" customHeight="1">
+    <x:row r="12" spans="1:1" ht="186.157227" customHeight="1">
       <x:c r="A12" s="13" t="s">
         <x:v>53</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" spans="1:1" ht="190.226207" customHeight="1">
+    <x:row r="13" spans="1:1" ht="204.772949" customHeight="1">
       <x:c r="A13" s="14" t="s">
         <x:v>54</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" spans="1:1" ht="207.519499" customHeight="1">
+    <x:row r="14" spans="1:1" ht="223.388672" customHeight="1">
       <x:c r="A14" s="15" t="s">
         <x:v>55</x:v>
       </x:c>
     </x:row>
-    <x:row r="15" spans="1:1" ht="224.81279" customHeight="1">
+    <x:row r="15" spans="1:1" ht="242.004395" customHeight="1">
       <x:c r="A15" s="16" t="s">
         <x:v>56</x:v>
       </x:c>
     </x:row>
-    <x:row r="16" spans="1:1" ht="242.106082" customHeight="1">
+    <x:row r="16" spans="1:1" ht="260.620117" customHeight="1">
       <x:c r="A16" s="17" t="s">
         <x:v>57</x:v>
       </x:c>
     </x:row>
-    <x:row r="17" spans="1:1" ht="259.399374" customHeight="1">
+    <x:row r="17" spans="1:1" ht="279.23584" customHeight="1">
       <x:c r="A17" s="18" t="s">
         <x:v>58</x:v>
       </x:c>
     </x:row>
-    <x:row r="18" spans="1:1" ht="276.692665" customHeight="1">
+    <x:row r="18" spans="1:1" ht="297.851562" customHeight="1">
       <x:c r="A18" s="19" t="s">
         <x:v>59</x:v>
       </x:c>
     </x:row>
-    <x:row r="19" spans="1:1" ht="293.985957" customHeight="1">
+    <x:row r="19" spans="1:1" ht="316.467285" customHeight="1">
       <x:c r="A19" s="20" t="s">
         <x:v>60</x:v>
       </x:c>

--- a/ClosedXML.Tests/Resource/Examples/Misc/AdjustToContents.xlsx
+++ b/ClosedXML.Tests/Resource/Examples/Misc/AdjustToContents.xlsx
@@ -3397,16 +3397,16 @@
   <x:dimension ref="A1:B8"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="30.790625" style="0" customWidth="1"/>
-    <x:col min="2" max="2" width="28.190625" style="0" customWidth="1"/>
+    <x:col min="1" max="1" width="30.890625" style="0" customWidth="1"/>
+    <x:col min="2" max="2" width="28.290625" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:2" ht="44.677734" customHeight="1">
+    <x:row r="1" spans="1:2" ht="37.5" customHeight="1">
       <x:c r="A1" s="1" t="s">
         <x:v>0</x:v>
       </x:c>
     </x:row>
-    <x:row r="2" spans="1:2" ht="29.785156" customHeight="1">
+    <x:row r="2" spans="1:2" ht="25" customHeight="1">
       <x:c r="A2" s="2" t="s">
         <x:v>1</x:v>
       </x:c>
@@ -3456,25 +3456,25 @@
   <x:dimension ref="A1:S1"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="2.930625" style="0" customWidth="1"/>
-    <x:col min="2" max="2" width="16.150625" style="0" customWidth="1"/>
-    <x:col min="3" max="3" width="17.315676" style="0" customWidth="1"/>
-    <x:col min="4" max="4" width="18.195145" style="0" customWidth="1"/>
-    <x:col min="5" max="5" width="17.902475" style="0" customWidth="1"/>
-    <x:col min="6" max="6" width="17.495861" style="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16.978396" style="0" customWidth="1"/>
-    <x:col min="8" max="8" width="16.354019" style="0" customWidth="1"/>
-    <x:col min="9" max="9" width="15.627482" style="0" customWidth="1"/>
-    <x:col min="10" max="10" width="14.804314" style="0" customWidth="1"/>
-    <x:col min="11" max="11" width="13.89078" style="0" customWidth="1"/>
-    <x:col min="12" max="12" width="12.893833" style="0" customWidth="1"/>
-    <x:col min="13" max="13" width="11.82106" style="0" customWidth="1"/>
-    <x:col min="14" max="14" width="10.680625" style="0" customWidth="1"/>
-    <x:col min="15" max="15" width="9.481208" style="0" customWidth="1"/>
-    <x:col min="16" max="16" width="8.231937" style="0" customWidth="1"/>
-    <x:col min="17" max="17" width="6.94232" style="0" customWidth="1"/>
-    <x:col min="18" max="18" width="5.622172" style="0" customWidth="1"/>
-    <x:col min="19" max="19" width="4.281539" style="0" customWidth="1"/>
+    <x:col min="1" max="1" width="3.020625" style="0" customWidth="1"/>
+    <x:col min="2" max="2" width="16.240625" style="0" customWidth="1"/>
+    <x:col min="3" max="3" width="17.495334" style="0" customWidth="1"/>
+    <x:col min="4" max="4" width="18.36393" style="0" customWidth="1"/>
+    <x:col min="5" max="5" width="18.069749" style="0" customWidth="1"/>
+    <x:col min="6" max="6" width="17.661036" style="0" customWidth="1"/>
+    <x:col min="7" max="7" width="17.1409" style="0" customWidth="1"/>
+    <x:col min="8" max="8" width="16.513301" style="0" customWidth="1"/>
+    <x:col min="9" max="9" width="15.783014" style="0" customWidth="1"/>
+    <x:col min="10" max="10" width="14.955597" style="0" customWidth="1"/>
+    <x:col min="11" max="11" width="14.037349" style="0" customWidth="1"/>
+    <x:col min="12" max="12" width="13.035256" style="0" customWidth="1"/>
+    <x:col min="13" max="13" width="11.956946" style="0" customWidth="1"/>
+    <x:col min="14" max="14" width="10.810625" style="0" customWidth="1"/>
+    <x:col min="15" max="15" width="9.605018" style="0" customWidth="1"/>
+    <x:col min="16" max="16" width="8.349299" style="0" customWidth="1"/>
+    <x:col min="17" max="17" width="7.053026" style="0" customWidth="1"/>
+    <x:col min="18" max="18" width="5.726064" style="0" customWidth="1"/>
+    <x:col min="19" max="19" width="4.378511" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:19">
@@ -3553,25 +3553,25 @@
   <x:dimension ref="A1:S1"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="2.930625" style="0" customWidth="1"/>
-    <x:col min="2" max="2" width="49.890625" style="0" customWidth="1"/>
-    <x:col min="3" max="3" width="60.107286" style="0" customWidth="1"/>
-    <x:col min="4" max="4" width="59.558663" style="0" customWidth="1"/>
-    <x:col min="5" max="5" width="58.648931" style="0" customWidth="1"/>
-    <x:col min="6" max="6" width="57.385015" style="0" customWidth="1"/>
-    <x:col min="7" max="7" width="55.776534" style="0" customWidth="1"/>
-    <x:col min="8" max="8" width="53.835729" style="0" customWidth="1"/>
-    <x:col min="9" max="9" width="51.57737" style="0" customWidth="1"/>
-    <x:col min="10" max="10" width="49.018646" style="0" customWidth="1"/>
-    <x:col min="11" max="11" width="46.17903" style="0" customWidth="1"/>
-    <x:col min="12" max="12" width="43.080132" style="0" customWidth="1"/>
-    <x:col min="13" max="13" width="39.745538" style="0" customWidth="1"/>
-    <x:col min="14" max="14" width="36.200625" style="0" customWidth="1"/>
-    <x:col min="15" max="15" width="32.472373" style="0" customWidth="1"/>
-    <x:col min="16" max="16" width="28.589156" style="0" customWidth="1"/>
-    <x:col min="17" max="17" width="24.580527" style="0" customWidth="1"/>
-    <x:col min="18" max="18" width="20.476994" style="0" customWidth="1"/>
-    <x:col min="19" max="19" width="16.309789" style="0" customWidth="1"/>
+    <x:col min="1" max="1" width="3.020625" style="0" customWidth="1"/>
+    <x:col min="2" max="2" width="49.930625" style="0" customWidth="1"/>
+    <x:col min="3" max="3" width="60.987133" style="0" customWidth="1"/>
+    <x:col min="4" max="4" width="60.438055" style="0" customWidth="1"/>
+    <x:col min="5" max="5" width="59.527568" style="0" customWidth="1"/>
+    <x:col min="6" max="6" width="58.262603" style="0" customWidth="1"/>
+    <x:col min="7" max="7" width="56.652786" style="0" customWidth="1"/>
+    <x:col min="8" max="8" width="54.71037" style="0" customWidth="1"/>
+    <x:col min="9" max="9" width="52.450137" style="0" customWidth="1"/>
+    <x:col min="10" max="10" width="49.889288" style="0" customWidth="1"/>
+    <x:col min="11" max="11" width="47.047314" style="0" customWidth="1"/>
+    <x:col min="12" max="12" width="43.945844" style="0" customWidth="1"/>
+    <x:col min="13" max="13" width="40.608481" style="0" customWidth="1"/>
+    <x:col min="14" max="14" width="37.060625" style="0" customWidth="1"/>
+    <x:col min="15" max="15" width="33.329278" style="0" customWidth="1"/>
+    <x:col min="16" max="16" width="29.442836" style="0" customWidth="1"/>
+    <x:col min="17" max="17" width="25.430879" style="0" customWidth="1"/>
+    <x:col min="18" max="18" width="21.32394" style="0" customWidth="1"/>
+    <x:col min="19" max="19" width="17.153275" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:19">
@@ -3650,97 +3650,97 @@
   <x:dimension ref="A1:A19"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
-    <x:row r="1" spans="1:1" ht="327.636719" customHeight="1">
+    <x:row r="1" spans="1:1" ht="275" customHeight="1">
       <x:c r="A1" s="3" t="s">
         <x:v>6</x:v>
       </x:c>
     </x:row>
-    <x:row r="2" spans="1:1" ht="16.381836" customHeight="1">
+    <x:row r="2" spans="1:1" ht="13.75" customHeight="1">
       <x:c r="A2" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
     </x:row>
-    <x:row r="3" spans="1:1" ht="8.190918" customHeight="1">
+    <x:row r="3" spans="1:1" ht="6.875" customHeight="1">
       <x:c r="A3" s="4" t="s">
         <x:v>8</x:v>
       </x:c>
     </x:row>
-    <x:row r="4" spans="1:1" ht="17.291938" customHeight="1">
+    <x:row r="4" spans="1:1" ht="14.513889" customHeight="1">
       <x:c r="A4" s="5" t="s">
         <x:v>9</x:v>
       </x:c>
     </x:row>
-    <x:row r="5" spans="1:1" ht="25.937907" customHeight="1">
+    <x:row r="5" spans="1:1" ht="21.770833" customHeight="1">
       <x:c r="A5" s="6" t="s">
         <x:v>10</x:v>
       </x:c>
     </x:row>
-    <x:row r="6" spans="1:1" ht="34.583876" customHeight="1">
+    <x:row r="6" spans="1:1" ht="29.027778" customHeight="1">
       <x:c r="A6" s="7" t="s">
         <x:v>11</x:v>
       </x:c>
     </x:row>
-    <x:row r="7" spans="1:1" ht="43.229845" customHeight="1">
+    <x:row r="7" spans="1:1" ht="36.284722" customHeight="1">
       <x:c r="A7" s="8" t="s">
         <x:v>12</x:v>
       </x:c>
     </x:row>
-    <x:row r="8" spans="1:1" ht="51.875814" customHeight="1">
+    <x:row r="8" spans="1:1" ht="43.541667" customHeight="1">
       <x:c r="A8" s="9" t="s">
         <x:v>13</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" spans="1:1" ht="60.521783" customHeight="1">
+    <x:row r="9" spans="1:1" ht="50.798611" customHeight="1">
       <x:c r="A9" s="10" t="s">
         <x:v>14</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" spans="1:1" ht="69.167752" customHeight="1">
+    <x:row r="10" spans="1:1" ht="58.055556" customHeight="1">
       <x:c r="A10" s="11" t="s">
         <x:v>15</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" spans="1:1" ht="77.813721" customHeight="1">
+    <x:row r="11" spans="1:1" ht="65.3125" customHeight="1">
       <x:c r="A11" s="12" t="s">
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" spans="1:1" ht="86.45969" customHeight="1">
+    <x:row r="12" spans="1:1" ht="72.569444" customHeight="1">
       <x:c r="A12" s="13" t="s">
         <x:v>17</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" spans="1:1" ht="95.105659" customHeight="1">
+    <x:row r="13" spans="1:1" ht="79.826389" customHeight="1">
       <x:c r="A13" s="14" t="s">
         <x:v>18</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" spans="1:1" ht="103.751628" customHeight="1">
+    <x:row r="14" spans="1:1" ht="87.083333" customHeight="1">
       <x:c r="A14" s="15" t="s">
         <x:v>19</x:v>
       </x:c>
     </x:row>
-    <x:row r="15" spans="1:1" ht="112.397597" customHeight="1">
+    <x:row r="15" spans="1:1" ht="94.340278" customHeight="1">
       <x:c r="A15" s="16" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
-    <x:row r="16" spans="1:1" ht="121.043566" customHeight="1">
+    <x:row r="16" spans="1:1" ht="101.597222" customHeight="1">
       <x:c r="A16" s="17" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
-    <x:row r="17" spans="1:1" ht="129.689535" customHeight="1">
+    <x:row r="17" spans="1:1" ht="108.854167" customHeight="1">
       <x:c r="A17" s="18" t="s">
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="18" spans="1:1" ht="138.335503" customHeight="1">
+    <x:row r="18" spans="1:1" ht="116.111111" customHeight="1">
       <x:c r="A18" s="19" t="s">
         <x:v>23</x:v>
       </x:c>
     </x:row>
-    <x:row r="19" spans="1:1" ht="146.981472" customHeight="1">
+    <x:row r="19" spans="1:1" ht="123.368056" customHeight="1">
       <x:c r="A19" s="20" t="s">
         <x:v>24</x:v>
       </x:c>
@@ -3762,97 +3762,97 @@
   <x:dimension ref="A1:A19"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
-    <x:row r="1" spans="1:1" ht="327.636719" customHeight="1">
+    <x:row r="1" spans="1:1" ht="275" customHeight="1">
       <x:c r="A1" s="3" t="s">
         <x:v>6</x:v>
       </x:c>
     </x:row>
-    <x:row r="2" spans="1:1" ht="89.355469" customHeight="1">
+    <x:row r="2" spans="1:1" ht="75" customHeight="1">
       <x:c r="A2" s="0" t="s">
         <x:v>43</x:v>
       </x:c>
     </x:row>
-    <x:row r="3" spans="1:1" ht="18.615723" customHeight="1">
+    <x:row r="3" spans="1:1" ht="15.625" customHeight="1">
       <x:c r="A3" s="4" t="s">
         <x:v>44</x:v>
       </x:c>
     </x:row>
-    <x:row r="4" spans="1:1" ht="37.231445" customHeight="1">
+    <x:row r="4" spans="1:1" ht="31.25" customHeight="1">
       <x:c r="A4" s="5" t="s">
         <x:v>45</x:v>
       </x:c>
     </x:row>
-    <x:row r="5" spans="1:1" ht="55.847168" customHeight="1">
+    <x:row r="5" spans="1:1" ht="46.875" customHeight="1">
       <x:c r="A5" s="6" t="s">
         <x:v>46</x:v>
       </x:c>
     </x:row>
-    <x:row r="6" spans="1:1" ht="74.462891" customHeight="1">
+    <x:row r="6" spans="1:1" ht="62.5" customHeight="1">
       <x:c r="A6" s="7" t="s">
         <x:v>47</x:v>
       </x:c>
     </x:row>
-    <x:row r="7" spans="1:1" ht="93.078613" customHeight="1">
+    <x:row r="7" spans="1:1" ht="78.125" customHeight="1">
       <x:c r="A7" s="8" t="s">
         <x:v>48</x:v>
       </x:c>
     </x:row>
-    <x:row r="8" spans="1:1" ht="111.694336" customHeight="1">
+    <x:row r="8" spans="1:1" ht="93.75" customHeight="1">
       <x:c r="A8" s="9" t="s">
         <x:v>49</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" spans="1:1" ht="130.310059" customHeight="1">
+    <x:row r="9" spans="1:1" ht="109.375" customHeight="1">
       <x:c r="A9" s="10" t="s">
         <x:v>50</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" spans="1:1" ht="148.925781" customHeight="1">
+    <x:row r="10" spans="1:1" ht="125" customHeight="1">
       <x:c r="A10" s="11" t="s">
         <x:v>51</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" spans="1:1" ht="167.541504" customHeight="1">
+    <x:row r="11" spans="1:1" ht="140.625" customHeight="1">
       <x:c r="A11" s="12" t="s">
         <x:v>52</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" spans="1:1" ht="186.157227" customHeight="1">
+    <x:row r="12" spans="1:1" ht="156.25" customHeight="1">
       <x:c r="A12" s="13" t="s">
         <x:v>53</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" spans="1:1" ht="204.772949" customHeight="1">
+    <x:row r="13" spans="1:1" ht="171.875" customHeight="1">
       <x:c r="A13" s="14" t="s">
         <x:v>54</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" spans="1:1" ht="223.388672" customHeight="1">
+    <x:row r="14" spans="1:1" ht="187.5" customHeight="1">
       <x:c r="A14" s="15" t="s">
         <x:v>55</x:v>
       </x:c>
     </x:row>
-    <x:row r="15" spans="1:1" ht="242.004395" customHeight="1">
+    <x:row r="15" spans="1:1" ht="203.125" customHeight="1">
       <x:c r="A15" s="16" t="s">
         <x:v>56</x:v>
       </x:c>
     </x:row>
-    <x:row r="16" spans="1:1" ht="260.620117" customHeight="1">
+    <x:row r="16" spans="1:1" ht="218.75" customHeight="1">
       <x:c r="A16" s="17" t="s">
         <x:v>57</x:v>
       </x:c>
     </x:row>
-    <x:row r="17" spans="1:1" ht="279.23584" customHeight="1">
+    <x:row r="17" spans="1:1" ht="234.375" customHeight="1">
       <x:c r="A17" s="18" t="s">
         <x:v>58</x:v>
       </x:c>
     </x:row>
-    <x:row r="18" spans="1:1" ht="297.851562" customHeight="1">
+    <x:row r="18" spans="1:1" ht="250" customHeight="1">
       <x:c r="A18" s="19" t="s">
         <x:v>59</x:v>
       </x:c>
     </x:row>
-    <x:row r="19" spans="1:1" ht="316.467285" customHeight="1">
+    <x:row r="19" spans="1:1" ht="265.625" customHeight="1">
       <x:c r="A19" s="20" t="s">
         <x:v>60</x:v>
       </x:c>

--- a/ClosedXML.Tests/Resource/Examples/Misc/AdjustToContents.xlsx
+++ b/ClosedXML.Tests/Resource/Examples/Misc/AdjustToContents.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="63">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:si>
     <x:t>Tall Row</x:t>
   </x:si>
@@ -3397,8 +3397,8 @@
   <x:dimension ref="A1:B8"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="30.890625" style="0" customWidth="1"/>
-    <x:col min="2" max="2" width="28.290625" style="0" customWidth="1"/>
+    <x:col min="1" max="1" width="31.710625" style="0" customWidth="1"/>
+    <x:col min="2" max="2" width="28.853482" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:2" ht="37.5" customHeight="1">
@@ -3406,7 +3406,7 @@
         <x:v>0</x:v>
       </x:c>
     </x:row>
-    <x:row r="2" spans="1:2" ht="25" customHeight="1">
+    <x:row r="2" spans="1:2" ht="25.5" customHeight="1">
       <x:c r="A2" s="2" t="s">
         <x:v>1</x:v>
       </x:c>
@@ -3456,25 +3456,24 @@
   <x:dimension ref="A1:S1"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="3.020625" style="0" customWidth="1"/>
-    <x:col min="2" max="2" width="16.240625" style="0" customWidth="1"/>
-    <x:col min="3" max="3" width="17.495334" style="0" customWidth="1"/>
-    <x:col min="4" max="4" width="18.36393" style="0" customWidth="1"/>
-    <x:col min="5" max="5" width="18.069749" style="0" customWidth="1"/>
-    <x:col min="6" max="6" width="17.661036" style="0" customWidth="1"/>
-    <x:col min="7" max="7" width="17.1409" style="0" customWidth="1"/>
-    <x:col min="8" max="8" width="16.513301" style="0" customWidth="1"/>
-    <x:col min="9" max="9" width="15.783014" style="0" customWidth="1"/>
-    <x:col min="10" max="10" width="14.955597" style="0" customWidth="1"/>
-    <x:col min="11" max="11" width="14.037349" style="0" customWidth="1"/>
-    <x:col min="12" max="12" width="13.035256" style="0" customWidth="1"/>
-    <x:col min="13" max="13" width="11.956946" style="0" customWidth="1"/>
-    <x:col min="14" max="14" width="10.810625" style="0" customWidth="1"/>
-    <x:col min="15" max="15" width="9.605018" style="0" customWidth="1"/>
-    <x:col min="16" max="16" width="8.349299" style="0" customWidth="1"/>
-    <x:col min="17" max="17" width="7.053026" style="0" customWidth="1"/>
-    <x:col min="18" max="18" width="5.726064" style="0" customWidth="1"/>
-    <x:col min="19" max="19" width="4.378511" style="0" customWidth="1"/>
+    <x:col min="1" max="1" width="1.853482" style="0" customWidth="1"/>
+    <x:col min="2" max="2" width="15.710625" style="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15.996339" style="0" customWidth="1"/>
+    <x:col min="4" max="5" width="16.996339" style="0" customWidth="1"/>
+    <x:col min="6" max="6" width="16.853482" style="0" customWidth="1"/>
+    <x:col min="7" max="7" width="16.567768" style="0" customWidth="1"/>
+    <x:col min="8" max="8" width="16.139196" style="0" customWidth="1"/>
+    <x:col min="9" max="9" width="15.567768" style="0" customWidth="1"/>
+    <x:col min="10" max="10" width="14.996339" style="0" customWidth="1"/>
+    <x:col min="11" max="11" width="14.282054" style="0" customWidth="1"/>
+    <x:col min="12" max="12" width="13.424911" style="0" customWidth="1"/>
+    <x:col min="13" max="13" width="12.567768" style="0" customWidth="1"/>
+    <x:col min="14" max="14" width="11.282054" style="0" customWidth="1"/>
+    <x:col min="15" max="15" width="10.282054" style="0" customWidth="1"/>
+    <x:col min="16" max="16" width="9.139196" style="0" customWidth="1"/>
+    <x:col min="17" max="17" width="7.853482" style="0" customWidth="1"/>
+    <x:col min="18" max="18" width="6.424911" style="0" customWidth="1"/>
+    <x:col min="19" max="19" width="5.139196" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:19">
@@ -3553,25 +3552,25 @@
   <x:dimension ref="A1:S1"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="3.020625" style="0" customWidth="1"/>
-    <x:col min="2" max="2" width="49.930625" style="0" customWidth="1"/>
-    <x:col min="3" max="3" width="60.987133" style="0" customWidth="1"/>
-    <x:col min="4" max="4" width="60.438055" style="0" customWidth="1"/>
-    <x:col min="5" max="5" width="59.527568" style="0" customWidth="1"/>
-    <x:col min="6" max="6" width="58.262603" style="0" customWidth="1"/>
-    <x:col min="7" max="7" width="56.652786" style="0" customWidth="1"/>
-    <x:col min="8" max="8" width="54.71037" style="0" customWidth="1"/>
-    <x:col min="9" max="9" width="52.450137" style="0" customWidth="1"/>
-    <x:col min="10" max="10" width="49.889288" style="0" customWidth="1"/>
-    <x:col min="11" max="11" width="47.047314" style="0" customWidth="1"/>
-    <x:col min="12" max="12" width="43.945844" style="0" customWidth="1"/>
-    <x:col min="13" max="13" width="40.608481" style="0" customWidth="1"/>
-    <x:col min="14" max="14" width="37.060625" style="0" customWidth="1"/>
-    <x:col min="15" max="15" width="33.329278" style="0" customWidth="1"/>
-    <x:col min="16" max="16" width="29.442836" style="0" customWidth="1"/>
-    <x:col min="17" max="17" width="25.430879" style="0" customWidth="1"/>
-    <x:col min="18" max="18" width="21.32394" style="0" customWidth="1"/>
-    <x:col min="19" max="19" width="17.153275" style="0" customWidth="1"/>
+    <x:col min="1" max="1" width="1.853482" style="0" customWidth="1"/>
+    <x:col min="2" max="2" width="51.282054" style="0" customWidth="1"/>
+    <x:col min="3" max="3" width="85.853482" style="0" customWidth="1"/>
+    <x:col min="4" max="4" width="86.424911" style="0" customWidth="1"/>
+    <x:col min="5" max="5" width="85.424911" style="0" customWidth="1"/>
+    <x:col min="6" max="6" width="83.710625" style="0" customWidth="1"/>
+    <x:col min="7" max="7" width="81.282054" style="0" customWidth="1"/>
+    <x:col min="8" max="8" width="78.424911" style="0" customWidth="1"/>
+    <x:col min="9" max="9" width="74.710625" style="0" customWidth="1"/>
+    <x:col min="10" max="10" width="70.567768" style="0" customWidth="1"/>
+    <x:col min="11" max="11" width="65.853482" style="0" customWidth="1"/>
+    <x:col min="12" max="12" width="60.710625" style="0" customWidth="1"/>
+    <x:col min="13" max="13" width="55.139196" style="0" customWidth="1"/>
+    <x:col min="14" max="14" width="49.282054" style="0" customWidth="1"/>
+    <x:col min="15" max="15" width="42.853482" style="0" customWidth="1"/>
+    <x:col min="16" max="16" width="35.996339" style="0" customWidth="1"/>
+    <x:col min="17" max="17" width="29.139196" style="0" customWidth="1"/>
+    <x:col min="18" max="18" width="21.710625" style="0" customWidth="1"/>
+    <x:col min="19" max="19" width="14.567768" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:19">
@@ -3650,97 +3649,97 @@
   <x:dimension ref="A1:A19"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
-    <x:row r="1" spans="1:1" ht="275" customHeight="1">
+    <x:row r="1" spans="1:1" ht="285" customHeight="1">
       <x:c r="A1" s="3" t="s">
         <x:v>6</x:v>
       </x:c>
     </x:row>
-    <x:row r="2" spans="1:1" ht="13.75" customHeight="1">
+    <x:row r="2" spans="1:1" ht="14.25" customHeight="1">
       <x:c r="A2" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
     </x:row>
-    <x:row r="3" spans="1:1" ht="6.875" customHeight="1">
+    <x:row r="3" spans="1:1" ht="21" customHeight="1">
       <x:c r="A3" s="4" t="s">
         <x:v>8</x:v>
       </x:c>
     </x:row>
-    <x:row r="4" spans="1:1" ht="14.513889" customHeight="1">
+    <x:row r="4" spans="1:1" ht="28.5" customHeight="1">
       <x:c r="A4" s="5" t="s">
         <x:v>9</x:v>
       </x:c>
     </x:row>
-    <x:row r="5" spans="1:1" ht="21.770833" customHeight="1">
+    <x:row r="5" spans="1:1" ht="34.5" customHeight="1">
       <x:c r="A5" s="6" t="s">
         <x:v>10</x:v>
       </x:c>
     </x:row>
-    <x:row r="6" spans="1:1" ht="29.027778" customHeight="1">
+    <x:row r="6" spans="1:1" ht="41.25" customHeight="1">
       <x:c r="A6" s="7" t="s">
         <x:v>11</x:v>
       </x:c>
     </x:row>
-    <x:row r="7" spans="1:1" ht="36.284722" customHeight="1">
+    <x:row r="7" spans="1:1" ht="47.25" customHeight="1">
       <x:c r="A7" s="8" t="s">
         <x:v>12</x:v>
       </x:c>
     </x:row>
-    <x:row r="8" spans="1:1" ht="43.541667" customHeight="1">
+    <x:row r="8" spans="1:1" ht="52.5" customHeight="1">
       <x:c r="A8" s="9" t="s">
         <x:v>13</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" spans="1:1" ht="50.798611" customHeight="1">
+    <x:row r="9" spans="1:1" ht="57.75" customHeight="1">
       <x:c r="A9" s="10" t="s">
         <x:v>14</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" spans="1:1" ht="58.055556" customHeight="1">
+    <x:row r="10" spans="1:1" ht="62.25" customHeight="1">
       <x:c r="A10" s="11" t="s">
         <x:v>15</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" spans="1:1" ht="65.3125" customHeight="1">
+    <x:row r="11" spans="1:1" ht="66.75" customHeight="1">
       <x:c r="A11" s="12" t="s">
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" spans="1:1" ht="72.569444" customHeight="1">
+    <x:row r="12" spans="1:1" ht="70.5" customHeight="1">
       <x:c r="A12" s="13" t="s">
         <x:v>17</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" spans="1:1" ht="79.826389" customHeight="1">
+    <x:row r="13" spans="1:1" ht="73.5" customHeight="1">
       <x:c r="A13" s="14" t="s">
         <x:v>18</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" spans="1:1" ht="87.083333" customHeight="1">
+    <x:row r="14" spans="1:1" ht="76.5" customHeight="1">
       <x:c r="A14" s="15" t="s">
         <x:v>19</x:v>
       </x:c>
     </x:row>
-    <x:row r="15" spans="1:1" ht="94.340278" customHeight="1">
+    <x:row r="15" spans="1:1" ht="78.75" customHeight="1">
       <x:c r="A15" s="16" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
-    <x:row r="16" spans="1:1" ht="101.597222" customHeight="1">
+    <x:row r="16" spans="1:1" ht="80.25" customHeight="1">
       <x:c r="A16" s="17" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
-    <x:row r="17" spans="1:1" ht="108.854167" customHeight="1">
+    <x:row r="17" spans="1:1" ht="81" customHeight="1">
       <x:c r="A17" s="18" t="s">
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="18" spans="1:1" ht="116.111111" customHeight="1">
+    <x:row r="18" spans="1:1" ht="81" customHeight="1">
       <x:c r="A18" s="19" t="s">
         <x:v>23</x:v>
       </x:c>
     </x:row>
-    <x:row r="19" spans="1:1" ht="123.368056" customHeight="1">
+    <x:row r="19" spans="1:1" ht="81" customHeight="1">
       <x:c r="A19" s="20" t="s">
         <x:v>24</x:v>
       </x:c>
@@ -3762,97 +3761,97 @@
   <x:dimension ref="A1:A19"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
-    <x:row r="1" spans="1:1" ht="275" customHeight="1">
+    <x:row r="1" spans="1:1" ht="285" customHeight="1">
       <x:c r="A1" s="3" t="s">
         <x:v>6</x:v>
       </x:c>
     </x:row>
-    <x:row r="2" spans="1:1" ht="75" customHeight="1">
+    <x:row r="2" spans="1:1" ht="59.25" customHeight="1">
       <x:c r="A2" s="0" t="s">
         <x:v>43</x:v>
       </x:c>
     </x:row>
-    <x:row r="3" spans="1:1" ht="15.625" customHeight="1">
+    <x:row r="3" spans="1:1" ht="47.25" customHeight="1">
       <x:c r="A3" s="4" t="s">
         <x:v>44</x:v>
       </x:c>
     </x:row>
-    <x:row r="4" spans="1:1" ht="31.25" customHeight="1">
+    <x:row r="4" spans="1:1" ht="75.75" customHeight="1">
       <x:c r="A4" s="5" t="s">
         <x:v>45</x:v>
       </x:c>
     </x:row>
-    <x:row r="5" spans="1:1" ht="46.875" customHeight="1">
+    <x:row r="5" spans="1:1" ht="102.75" customHeight="1">
       <x:c r="A5" s="6" t="s">
         <x:v>46</x:v>
       </x:c>
     </x:row>
-    <x:row r="6" spans="1:1" ht="62.5" customHeight="1">
+    <x:row r="6" spans="1:1" ht="129.75" customHeight="1">
       <x:c r="A6" s="7" t="s">
         <x:v>47</x:v>
       </x:c>
     </x:row>
-    <x:row r="7" spans="1:1" ht="78.125" customHeight="1">
+    <x:row r="7" spans="1:1" ht="155.25" customHeight="1">
       <x:c r="A7" s="8" t="s">
         <x:v>48</x:v>
       </x:c>
     </x:row>
-    <x:row r="8" spans="1:1" ht="93.75" customHeight="1">
+    <x:row r="8" spans="1:1" ht="180" customHeight="1">
       <x:c r="A8" s="9" t="s">
         <x:v>49</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" spans="1:1" ht="109.375" customHeight="1">
+    <x:row r="9" spans="1:1" ht="203.25" customHeight="1">
       <x:c r="A9" s="10" t="s">
         <x:v>50</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" spans="1:1" ht="125" customHeight="1">
+    <x:row r="10" spans="1:1" ht="225" customHeight="1">
       <x:c r="A10" s="11" t="s">
         <x:v>51</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" spans="1:1" ht="140.625" customHeight="1">
+    <x:row r="11" spans="1:1" ht="244.5" customHeight="1">
       <x:c r="A11" s="12" t="s">
         <x:v>52</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" spans="1:1" ht="156.25" customHeight="1">
+    <x:row r="12" spans="1:1" ht="263.25" customHeight="1">
       <x:c r="A12" s="13" t="s">
         <x:v>53</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" spans="1:1" ht="171.875" customHeight="1">
+    <x:row r="13" spans="1:1" ht="279" customHeight="1">
       <x:c r="A13" s="14" t="s">
         <x:v>54</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" spans="1:1" ht="187.5" customHeight="1">
+    <x:row r="14" spans="1:1" ht="293.25" customHeight="1">
       <x:c r="A14" s="15" t="s">
         <x:v>55</x:v>
       </x:c>
     </x:row>
-    <x:row r="15" spans="1:1" ht="203.125" customHeight="1">
+    <x:row r="15" spans="1:1" ht="304.5" customHeight="1">
       <x:c r="A15" s="16" t="s">
         <x:v>56</x:v>
       </x:c>
     </x:row>
-    <x:row r="16" spans="1:1" ht="218.75" customHeight="1">
+    <x:row r="16" spans="1:1" ht="314.25" customHeight="1">
       <x:c r="A16" s="17" t="s">
         <x:v>57</x:v>
       </x:c>
     </x:row>
-    <x:row r="17" spans="1:1" ht="234.375" customHeight="1">
+    <x:row r="17" spans="1:1" ht="321" customHeight="1">
       <x:c r="A17" s="18" t="s">
         <x:v>58</x:v>
       </x:c>
     </x:row>
-    <x:row r="18" spans="1:1" ht="250" customHeight="1">
+    <x:row r="18" spans="1:1" ht="325.5" customHeight="1">
       <x:c r="A18" s="19" t="s">
         <x:v>59</x:v>
       </x:c>
     </x:row>
-    <x:row r="19" spans="1:1" ht="265.625" customHeight="1">
+    <x:row r="19" spans="1:1" ht="327.75" customHeight="1">
       <x:c r="A19" s="20" t="s">
         <x:v>60</x:v>
       </x:c>
@@ -3874,7 +3873,7 @@
   <x:dimension ref="A1:B1"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="11.920625" style="0" customWidth="1"/>
+    <x:col min="1" max="1" width="11.424911" style="0" customWidth="1"/>
     <x:col min="2" max="2" width="255" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>

--- a/ClosedXML.Tests/Resource/Examples/Misc/AdjustToContents.xlsx
+++ b/ClosedXML.Tests/Resource/Examples/Misc/AdjustToContents.xlsx
@@ -3390,7 +3390,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
@@ -3449,7 +3449,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
@@ -3545,7 +3545,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
@@ -3642,7 +3642,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
@@ -3754,7 +3754,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
@@ -3866,7 +3866,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>

--- a/ClosedXML.Tests/Resource/Examples/Misc/AdjustToContents.xlsx
+++ b/ClosedXML.Tests/Resource/Examples/Misc/AdjustToContents.xlsx
@@ -6,12 +6,12 @@
     <x:workbookView firstSheet="0" activeTab="0"/>
   </x:bookViews>
   <x:sheets>
-    <x:sheet name="Adjust To Contents" sheetId="2" r:id="rId2"/>
-    <x:sheet name="Adjust Widths" sheetId="3" r:id="rId3"/>
-    <x:sheet name="Adjust Widths 2" sheetId="4" r:id="rId4"/>
-    <x:sheet name="Adjust Heights" sheetId="5" r:id="rId5"/>
-    <x:sheet name="Adjust Heights 2" sheetId="6" r:id="rId6"/>
-    <x:sheet name="Absurdly wide column" sheetId="7" r:id="rId7"/>
+    <x:sheet name="Adjust To Contents" sheetId="1" r:id="rId2"/>
+    <x:sheet name="Adjust Widths" sheetId="2" r:id="rId3"/>
+    <x:sheet name="Adjust Widths 2" sheetId="3" r:id="rId4"/>
+    <x:sheet name="Adjust Heights" sheetId="4" r:id="rId5"/>
+    <x:sheet name="Adjust Heights 2" sheetId="5" r:id="rId6"/>
+    <x:sheet name="Absurdly wide column" sheetId="6" r:id="rId7"/>
   </x:sheets>
   <x:definedNames/>
   <x:calcPr calcId="125725"/>
